--- a/test-dan/ig/StructureDefinition-CapaciteActiviteExercee.xlsx
+++ b/test-dan/ig/StructureDefinition-CapaciteActiviteExercee.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T13:42:24+00:00</t>
+    <t>2026-03-12T13:48:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
